--- a/processo_2/synthetic_proposals/PROPOSTA_020/ficha_pontuacao.xlsx
+++ b/processo_2/synthetic_proposals/PROPOSTA_020/ficha_pontuacao.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Peso (valor)</t>
+          <t>Pontos</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr"/>
     </row>
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>2.5</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="inlineStr"/>
     </row>
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>1.5</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr"/>
     </row>
@@ -680,17 +680,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G12" t="inlineStr"/>
     </row>
@@ -703,17 +703,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G13" t="inlineStr"/>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -749,7 +749,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -804,29 +804,21 @@
           <t>Revista Científica Avançada 1</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1339-3307</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Revista Científica Avançada 2</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>68%</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -966,7 +958,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -989,7 +981,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1058,17 +1050,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr"/>
     </row>
@@ -1083,7 +1075,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
@@ -1126,17 +1118,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="inlineStr"/>
     </row>
@@ -1149,7 +1141,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1176,13 +1168,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
         <v>20</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G36" t="inlineStr"/>
     </row>
@@ -1195,7 +1187,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1218,7 +1210,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1241,7 +1233,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1264,17 +1256,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr"/>
     </row>
@@ -1287,7 +1279,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1310,17 +1302,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>1.5</v>
       </c>
       <c r="F42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr"/>
     </row>
@@ -1333,7 +1325,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1377,13 +1369,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G45" t="inlineStr"/>
     </row>
@@ -1423,13 +1415,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G47" t="inlineStr"/>
     </row>
@@ -1551,7 +1543,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1574,7 +1566,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1620,17 +1612,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>10</v>
       </c>
       <c r="F56" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G56" t="inlineStr"/>
     </row>
@@ -1643,7 +1635,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1668,7 +1660,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>20.5</v>
+        <v>41</v>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
@@ -1738,13 +1730,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
         <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G62" t="inlineStr"/>
     </row>
@@ -1761,13 +1753,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
         <v>4</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G63" t="inlineStr"/>
     </row>
@@ -1784,13 +1776,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
         <v>4</v>
       </c>
       <c r="F64" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G64" t="inlineStr"/>
     </row>
@@ -1851,7 +1843,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G67" t="inlineStr"/>
     </row>
@@ -1866,7 +1858,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>46</v>
+        <v>55.5</v>
       </c>
       <c r="G68" t="inlineStr"/>
     </row>
